--- a/artfynd/A 3253-2025 artfynd.xlsx
+++ b/artfynd/A 3253-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1171,507 +1171,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>91510513</v>
-      </c>
-      <c r="B6" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>100067</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Havsörn</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Haliaeetus albicilla</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Brov ägs mitt, Sk</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>430293.528510611</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6152759.940460711</v>
-      </c>
-      <c r="S6" t="n">
-        <v>25</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Ystad</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Högestad</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2021-03-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2021-03-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Marie-Louise Bárány</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Marie-Louise Bárány</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>92294820</v>
-      </c>
-      <c r="B7" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>100048</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Dryobates minor</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Brov ägs mitt, Sk</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>430293.528510611</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6152759.940460711</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Ystad</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Högestad</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2021-04-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2021-04-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Trumning</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Marie-Louise Bárány</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Marie-Louise Bárány</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>92294819</v>
-      </c>
-      <c r="B8" t="n">
-        <v>56812</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>102999</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Björktrast</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Turdus pilaris</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Brov ägs mitt, Sk</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>430293.528510611</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6152759.940460711</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Ystad</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Högestad</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2021-04-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2021-04-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Marie-Louise Bárány</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Marie-Louise Bárány</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>92294811</v>
-      </c>
-      <c r="B9" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Brov ägs mitt, Sk</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>430293.528510611</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6152759.940460711</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Ystad</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Högestad</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2021-04-09</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2021-04-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Marie-Louise Bárány</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Marie-Louise Bárány</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3253-2025 artfynd.xlsx
+++ b/artfynd/A 3253-2025 artfynd.xlsx
@@ -918,12 +918,7 @@
         <v>270567</v>
       </c>
       <c r="B4" t="n">
-        <v>97512</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -955,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430042.0212686392</v>
+        <v>430042</v>
       </c>
       <c r="R4" t="n">
-        <v>6152713.557101772</v>
+        <v>6152714</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -985,7 +980,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>M-Ysd-0042</t>
+          <t>Arkiv-M-Ysd-0044</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -993,19 +988,9 @@
           <t>1991-08-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1991-08-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,7 +1014,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Lund-Botaniska/Zoologiska museet</t>
+          <t>Biologiska Museet, Lunds Universitet</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr"/>
@@ -1046,7 +1031,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 3253-2025 artfynd.xlsx
+++ b/artfynd/A 3253-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>270567</v>
       </c>
       <c r="B4" t="n">
-        <v>100139</v>
+        <v>100142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3253-2025 artfynd.xlsx
+++ b/artfynd/A 3253-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>270567</v>
       </c>
       <c r="B4" t="n">
-        <v>100142</v>
+        <v>100168</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3253-2025 artfynd.xlsx
+++ b/artfynd/A 3253-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>270567</v>
       </c>
       <c r="B4" t="n">
-        <v>100168</v>
+        <v>100169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3253-2025 artfynd.xlsx
+++ b/artfynd/A 3253-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>270567</v>
       </c>
       <c r="B4" t="n">
-        <v>100169</v>
+        <v>100170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3253-2025 artfynd.xlsx
+++ b/artfynd/A 3253-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>270567</v>
       </c>
       <c r="B4" t="n">
-        <v>100170</v>
+        <v>100172</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3253-2025 artfynd.xlsx
+++ b/artfynd/A 3253-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>270567</v>
       </c>
       <c r="B4" t="n">
-        <v>100172</v>
+        <v>100176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3253-2025 artfynd.xlsx
+++ b/artfynd/A 3253-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>270567</v>
       </c>
       <c r="B4" t="n">
-        <v>100176</v>
+        <v>100189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3253-2025 artfynd.xlsx
+++ b/artfynd/A 3253-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>270567</v>
       </c>
       <c r="B4" t="n">
-        <v>100189</v>
+        <v>100190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3253-2025 artfynd.xlsx
+++ b/artfynd/A 3253-2025 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>270567</v>
       </c>
       <c r="B4" t="n">
-        <v>100190</v>
+        <v>100193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 3253-2025 artfynd.xlsx
+++ b/artfynd/A 3253-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2130954</v>
+        <v>270567</v>
       </c>
       <c r="B2" t="n">
-        <v>77881</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100346</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6431</v>
+        <v>174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fyledalen, Sk</t>
+          <t>Åhuset, 300 m NV, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>430077.9909014857</v>
+        <v>430042</v>
       </c>
       <c r="R2" t="n">
-        <v>6152763.369284536</v>
+        <v>6152714</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,29 +738,24 @@
           <t>Högestad</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Arkiv-M-Ysd-0044</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-07-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1991-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1991-08-07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>2D1f0641</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,30 +767,40 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>fuktig lövlund</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Dahlberg</t>
+          <t>Skåne Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Skåne Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2132171</v>
+        <v>2130954</v>
       </c>
       <c r="B3" t="n">
-        <v>77881</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430073.5353825133</v>
+        <v>430078</v>
       </c>
       <c r="R3" t="n">
-        <v>6152804.20109223</v>
+        <v>6152763</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +862,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-07-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-07-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-07-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-07-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ask</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,17 +884,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Johan Dahlberg</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -915,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>270567</v>
+        <v>2132171</v>
       </c>
       <c r="B4" t="n">
-        <v>100193</v>
+        <v>79707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,37 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>174</v>
+        <v>6431</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Åhuset, 300 m NV, Sk</t>
+          <t>Fyledalen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430042</v>
+        <v>430074</v>
       </c>
       <c r="R4" t="n">
-        <v>6152714</v>
+        <v>6152804</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,24 +962,14 @@
           <t>Högestad</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Arkiv-M-Ysd-0044</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1991-08-07</t>
+          <t>2010-07-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1991-08-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2D1f0641</t>
+          <t>2010-07-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,154 +981,29 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>fuktig lövlund</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Biologiska Museet, Lunds Universitet</t>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Johan Dahlberg</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Skåne Floraväktarna</t>
+          <t>Johan Dahlberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Skåne Floraväktarna</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>7072523</v>
-      </c>
-      <c r="B5" t="n">
-        <v>92722</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1136</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Gotländsk hättemossa</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Orthotrichum rogeri</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Brid.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Åhuset, N om, Fyledelen, Sk</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>430075.8753902946</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6152773.027106597</v>
-      </c>
-      <c r="S5" t="n">
-        <v>50</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Ystad</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Högestad</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2013-11-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2013-11-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Vägträd, ask, hästkastanj</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>BGM – tre mossor 2013</t>
-        </is>
-      </c>
+          <t>Johan Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3253-2025 artfynd.xlsx
+++ b/artfynd/A 3253-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/270567</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2130954</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,8 +1019,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2132171</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>